--- a/Tools/Model_lookup.xlsx
+++ b/Tools/Model_lookup.xlsx
@@ -65,565 +65,565 @@
     <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
   </si>
   <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alp_Past_Shrubland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shrubland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed_Forest_Open_Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed_Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glacier_Static</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glacier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Glacier.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Glacier.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland_Int_AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int_AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland_Open_Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland_Perm_crops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perm_crops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grassland_Urban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Int_AG_Grassland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Int_AG.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Int_AG.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">Alp_Past_Shrubland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shrubland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Int_AG_Perm_crops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">14</t>
   </si>
   <si>
-    <t xml:space="preserve">Closed_Forest_Open_Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed_Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Int_AG_Urban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Int_AG.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Int_AG.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open_Forest_Alp_Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">06</t>
   </si>
   <si>
-    <t xml:space="preserve">Glacier_Static</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glacier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Glacier.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Glacier.Static.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Open_Forest_Closed_Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open_Forest_Grassland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Open_Forest.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Open_Forest.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perm_crops_Grassland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Perm_crops.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Perm_crops.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perm_crops_Int_AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">22</t>
   </si>
   <si>
-    <t xml:space="preserve">Grassland_Int_AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grassland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int_AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grassland_Open_Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grassland_Perm_crops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perm_crops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grassland_Urban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Grassland.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Grassland.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int_AG_Grassland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Int_AG.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Int_AG.Grassland.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Perm_crops_Urban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Perm_crops.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Perm_crops.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shrubland_Alp_Past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">11</t>
   </si>
   <si>
-    <t xml:space="preserve">Int_AG_Perm_crops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Int_AG_Urban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Int_AG.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Int_AG.Urban.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Shrubland_Closed_Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">10</t>
   </si>
   <si>
-    <t xml:space="preserve">Open_Forest_Alp_Past</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Shrubland_Open_Forest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Static_Shrubland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Static.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Static.Shrubland.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">04</t>
   </si>
   <si>
-    <t xml:space="preserve">Open_Forest_Closed_Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Urban_Static</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eastern_Central_Alps.Urban.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Urban.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Grassland.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Grassland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Grassland.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Grassland.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Int_AG.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Int_AG.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Int_AG.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Int_AG.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Int_AG.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Int_AG.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Open_Forest.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Open_Forest.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Perm_crops.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Perm_crops.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Perm_crops.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Perm_crops.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Perm_crops.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Perm_crops.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Shrubland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Shrubland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Static.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Static.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban_Int_AG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura.Urban.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Urban.Int_AG.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">03</t>
   </si>
   <si>
-    <t xml:space="preserve">Open_Forest_Grassland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Open_Forest.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Open_Forest.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perm_crops_Grassland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Perm_crops.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Perm_crops.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perm_crops_Int_AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perm_crops_Urban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Perm_crops.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Perm_crops.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shrubland_Alp_Past</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shrubland_Closed_Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shrubland_Open_Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static_Shrubland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Static.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Static.Shrubland.2009_2018.rf.rds</t>
+    <t xml:space="preserve">Jura.Urban.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Urban.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Glacier.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Glacier.Static.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Grassland.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Grassland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Grassland.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Grassland.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Int_AG.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Int_AG.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Int_AG.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Int_AG.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Open_Forest.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Open_Forest.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Perm_crops.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Perm_crops.Grassland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Perm_crops.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Perm_crops.Urban.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Static.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Static.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Urban.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Urban.Int_AG.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban_Shrubland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern_Prealps.Urban.Shrubland.2009_2018.rf.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Urban.Shrubland.2009_2018.rf.rds</t>
   </si>
   <si>
     <t xml:space="preserve">02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban_Static</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eastern_Central_Alps.Urban.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Eastern_Central_Alps.Urban.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Alp_Past.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Alp_Past.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Grassland.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Grassland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Grassland.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Grassland.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Grassland.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Int_AG.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Int_AG.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Int_AG.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Int_AG.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Int_AG.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Int_AG.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Open_Forest.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Open_Forest.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Perm_crops.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Perm_crops.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Perm_crops.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Perm_crops.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Perm_crops.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Perm_crops.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Shrubland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Shrubland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Static.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Static.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban_Int_AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Urban.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Urban.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jura.Urban.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Jura.Urban.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Alp_Past.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Alp_Past.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Closed_Forest.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Glacier.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Glacier.Static.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Grassland.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Grassland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Grassland.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Grassland.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Grassland.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Int_AG.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Int_AG.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Int_AG.Perm_crops.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Int_AG.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Int_AG.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Open_Forest.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Open_Forest.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Open_Forest.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Open_Forest.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Perm_crops.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Perm_crops.Grassland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Perm_crops.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Perm_crops.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Perm_crops.Urban.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Shrubland.Alp_Past.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Shrubland.Closed_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Shrubland.Open_Forest.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Static.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Static.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Urban.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Urban.Int_AG.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urban_Shrubland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern_Prealps.Urban.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data/Transition_models/Prediction_models/2009_2018/Northern_Prealps.Urban.Shrubland.2009_2018.rf.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
   </si>
   <si>
     <t xml:space="preserve">Northern_Prealps.Urban.Static.2009_2018.rf.rds</t>
